--- a/Thermomix TM6/Grading/2 stage/6-examples/Thermomix-TM6_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Thermomix TM6/Grading/2 stage/6-examples/Thermomix-TM6_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="16180" yWindow="-21600" windowWidth="38400" windowHeight="21600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Thermonix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gemini Generation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Thermonix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C1" s="14" t="inlineStr">
         <is>
-          <t>GPT-5</t>
+          <t>Grading</t>
         </is>
       </c>
       <c r="D1" s="14" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>Initial state correctly transitions to TransportationMode</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>TransportationMode state is present</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Transition from TransportationMode to On via selectorPressed is present with deactivation action</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>Represented by ShutdownMessage state which shows switching off message after 5sec hold</t>
+          <t>Represented as SwitchingOff</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>ShutdownMessage transitions to Off on selectorReleased; the holding states return to Operating on early release preserving On context</t>
+          <t>Implicitly and correctly handled by the time &gt;= 5s guard on the transition to SwitchingOff</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>HoldingFromHome and similar states transition to ShutdownMessage after 5sec which then leads to Off</t>
+          <t>Represented by the time &gt;= 5s guard and subsequent selectorReleased transition</t>
         </is>
       </c>
     </row>
@@ -5954,7 +5954,7 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Off state is present</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Transition from Off to On via selectorPressed is present</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -5994,7 +5994,7 @@
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>On is a composite state containing Operating and other substates</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -6010,11 +6010,11 @@
         </is>
       </c>
       <c r="C11" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>History state H is present in RecipeExecution and used to restore context after early selector release</t>
+          <t>Missing history state</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Multiple holding states (HoldingFromHome etc) capture selectorHeld from various Operating substates leading to shutdown sequence</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>MealReady transitions to Home on bowlRemoved which stays within On composite state</t>
+          <t>Represented by transitions from Cooking and ShutdownWarning to HomeScreen</t>
         </is>
       </c>
     </row>
@@ -6066,7 +6066,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Initial State (On ⇒  Home)</t>
+          <t>Initial State (On ⇒ Home)</t>
         </is>
       </c>
       <c r="C14" s="15" t="n">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>On composite state has initial transition to Operating which has initial transition to Home</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Home state is present within Operating</t>
+          <t>Represented as HomeScreen</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
-          <t>Operating transitions to AutoShutdownWarning after 14min30sec when notInUse</t>
+          <t>Correctly represented</t>
         </is>
       </c>
       <c r="E16" s="5" t="n"/>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>RecipeSelected transitions to RecipeExecution on start which begins at AddIngredients (prompt to add)</t>
+          <t>Represented via RecipeSelected intermediate state</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
-          <t>Guard bowlPlaced() is used on start transition; semantically equivalent to checking bowl is present</t>
+          <t>Represented as bowlPlaced guard</t>
         </is>
       </c>
     </row>
@@ -6188,11 +6188,11 @@
         </is>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>instructAddIngredients(recipeStep) action captures setting up ingredient prompts</t>
+          <t>Represented as weighIngredients do-action in AddIngredients state</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
-          <t>AutoShutdownWarning state represents preparing shutdown with 30sec countdown</t>
+          <t>Represented as ShutdownWarning</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>AutoShutdownWarning transitions to Off after 30sec with powerOff action</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -6252,7 +6252,7 @@
       </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
-          <t>AutoShutdownWarning transitions to Operating on cancel which returns to Home</t>
+          <t>Correctly represented</t>
         </is>
       </c>
       <c r="E22" s="5" t="n"/>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>AddIngredients state represents prompting to add ingredients</t>
+          <t>Represented as AddIngredients</t>
         </is>
       </c>
     </row>
@@ -6306,11 +6306,11 @@
         </is>
       </c>
       <c r="C24" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
-          <t>Cooking transitions back to AddIngredients when hasMoreRecipeSteps after cooking done</t>
+          <t>Missing self-transition for adding more ingredients</t>
         </is>
       </c>
     </row>
@@ -6326,11 +6326,11 @@
         </is>
       </c>
       <c r="C25" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="18" t="inlineStr">
         <is>
-          <t>correctAmountAdded event and hasMoreRecipeSteps guard capture weight correctness and more ingredients logic</t>
+          <t>Missing guard for more ingredients</t>
         </is>
       </c>
     </row>
@@ -6346,11 +6346,11 @@
         </is>
       </c>
       <c r="C26" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="18" t="inlineStr">
         <is>
-          <t>advanceRecipeStep() action when returning to AddIngredients captures setting next ingredients</t>
+          <t>Missing action</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>IngredientsAmountConfirmed transitions to Chopping on next event</t>
+          <t>Correctly represented</t>
         </is>
       </c>
     </row>
@@ -6386,11 +6386,11 @@
         </is>
       </c>
       <c r="C28" s="17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D28" s="18" t="inlineStr">
         <is>
-          <t>correctAmountAdded event enables next step; flow proceeds to chopping when amount confirmed</t>
+          <t>Partially represented by correctAmountAdded guard but missing moreIngredientsRequired check</t>
         </is>
       </c>
     </row>
@@ -6406,11 +6406,11 @@
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>startChopping(recipeSpeed recipeChopTime) action captures setting chopping parameters</t>
+          <t>Represented as chopIngredients do-action in Chopping state</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="D30" s="18" t="inlineStr">
         <is>
-          <t>Chopping state is present</t>
+          <t>Represented as Chopping</t>
         </is>
       </c>
     </row>
@@ -6446,11 +6446,11 @@
         </is>
       </c>
       <c r="C31" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Cooking can transition back to AddIngredients when more steps exist after cooking</t>
+          <t>Missing transition back to AddIngredients from Chopping</t>
         </is>
       </c>
     </row>
@@ -6466,11 +6466,11 @@
         </is>
       </c>
       <c r="C32" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="18" t="inlineStr">
         <is>
-          <t>choppingDone event and hasMoreRecipeSteps logic capture chopping completion and more ingredients needed</t>
+          <t>Missing guard</t>
         </is>
       </c>
     </row>
@@ -6486,11 +6486,11 @@
         </is>
       </c>
       <c r="C33" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>advanceRecipeStep() when transitioning back to AddIngredients sets next ingredients</t>
+          <t>Missing action</t>
         </is>
       </c>
       <c r="E33" s="5" t="n"/>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="D34" s="18" t="inlineStr">
         <is>
-          <t>ReadyForCooking transitions to Cooking on next event when bowl is placed</t>
+          <t>Represented via ChoppingDone intermediate state</t>
         </is>
       </c>
     </row>
@@ -6544,11 +6544,11 @@
         </is>
       </c>
       <c r="C35" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>choppingDone leads to ReadyForCooking; next proceeds to Cooking when ready</t>
+          <t>Partially represented by choppingCompleted event but missing moreIngredientsRequired check</t>
         </is>
       </c>
       <c r="E35" s="5" t="n"/>
@@ -6582,11 +6582,11 @@
         </is>
       </c>
       <c r="C36" s="17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D36" s="18" t="inlineStr">
         <is>
-          <t>startCooking(recipeTemperature recipeCookTime) action captures setting cooking parameters</t>
+          <t>Represented as cookMeal do-action in CookingStep state</t>
         </is>
       </c>
       <c r="E36" s="5" t="n"/>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>Cooking state is present</t>
+          <t>Represented as CookingStep</t>
         </is>
       </c>
       <c r="E37" s="5" t="n"/>
@@ -6658,11 +6658,11 @@
         </is>
       </c>
       <c r="C38" s="17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D38" s="18" t="inlineStr">
         <is>
-          <t>Cooking transitions to AddIngredients on cookingDone not after choppingTime; timing mechanism differs but loop behavior partially captured</t>
+          <t>Represented by transition from CookingDone to AddIngredients</t>
         </is>
       </c>
       <c r="E38" s="5" t="n"/>
@@ -6696,11 +6696,11 @@
         </is>
       </c>
       <c r="C39" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>cookingDone with hasMoreRecipeSteps guard captures completion and more ingredients logic</t>
+          <t>Represented as promptAddIngredients event instead of a guard</t>
         </is>
       </c>
       <c r="E39" s="5" t="n"/>
@@ -6734,11 +6734,11 @@
         </is>
       </c>
       <c r="C40" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40" s="18" t="inlineStr">
         <is>
-          <t>advanceRecipeStep() action sets next ingredients when looping back</t>
+          <t>Missing action</t>
         </is>
       </c>
       <c r="E40" s="5" t="n"/>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Cooking transitions to MealReady on cookingDone when isLastRecipeStep</t>
+          <t>Represented by transition from CookingDone to MealReady</t>
         </is>
       </c>
       <c r="E41" s="5" t="n"/>
@@ -6810,11 +6810,11 @@
         </is>
       </c>
       <c r="C42" s="17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D42" s="18" t="inlineStr">
         <is>
-          <t>isLastRecipeStep guard is semantically equivalent to no more ingredients required</t>
+          <t>Represented as lastStepCompleted event instead of a guard</t>
         </is>
       </c>
       <c r="E42" s="5" t="n"/>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>MealReady state represents meal ready</t>
+          <t>Represented as MealReady</t>
         </is>
       </c>
       <c r="E43" s="5" t="n"/>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="D44" s="20" t="inlineStr">
         <is>
-          <t>No auto-shutdown timer from MealReady state; only from Operating level</t>
+          <t>Missing transition from MealReady to ShutdownWarning</t>
         </is>
       </c>
       <c r="E44" s="5" t="n"/>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="D45" s="22" t="inlineStr">
         <is>
-          <t>RecipeSelected and intermediate states are reasonable modeling choices that preserve system behavior</t>
+          <t>Intermediate states are reasonable modeling choices</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>Additional transitions for holding states and bowl placement checks are reasonable and preserve correctness</t>
+          <t>Transitions for intermediate states are reasonable</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="D47" s="22" t="inlineStr">
         <is>
-          <t>Additional guards like heldLessThan5sec and bowlPlaced are reasonable refinements of system logic</t>
+          <t>No fundamentally incorrect guards</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="D48" s="24" t="inlineStr">
         <is>
-          <t>Additional actions like enableNextStep and loadRecipeSteps are reasonable implementation details</t>
+          <t>No fundamentally incorrect actions</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="D49" s="22" t="inlineStr">
         <is>
-          <t>Operating and RecipeExecution composite states are reasonable structural choices</t>
+          <t>Cooking composite state is a reasonable abstraction</t>
         </is>
       </c>
     </row>
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D50" s="24" t="inlineStr">
         <is>
-          <t>No additional regions present</t>
+          <t>No additional regions</t>
         </is>
       </c>
     </row>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="D51" s="22" t="inlineStr">
         <is>
-          <t>History state H is appropriately used for context restoration</t>
+          <t>No additional history states</t>
         </is>
       </c>
     </row>
@@ -10865,7 +10865,7 @@
     <row r="1" ht="15.75" customHeight="1" s="65">
       <c r="A1" s="66" t="inlineStr">
         <is>
-          <t>Generated by GPT-5</t>
+          <t>Generated by Gemini 3.1 Pro</t>
         </is>
       </c>
       <c r="J1" s="27" t="inlineStr">
@@ -10932,15 +10932,15 @@
         <v/>
       </c>
       <c r="C3" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$44, $A3, 'GPT-5 Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D3" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$45:$A$51, $A3, 'GPT-5 Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A3, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E3" s="31">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$44, $A3, 'GPT-5 Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F3" s="31">
@@ -10968,15 +10968,15 @@
         <v/>
       </c>
       <c r="C4" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$44, $A4, 'GPT-5 Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D4" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$45:$A$51, $A4, 'GPT-5 Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A4, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E4" s="31">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$44, $A4, 'GPT-5 Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F4" s="31">
@@ -11008,15 +11008,15 @@
         <v/>
       </c>
       <c r="C5" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$44, $A5, 'GPT-5 Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D5" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$45:$A$51, $A5, 'GPT-5 Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A5, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E5" s="31">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$44, $A5, 'GPT-5 Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F5" s="31">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="J5" s="22" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -11048,15 +11048,15 @@
         <v/>
       </c>
       <c r="C6" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$44, $A6, 'GPT-5 Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D6" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$45:$A$51, $A6, 'GPT-5 Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A6, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E6" s="31">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$44, $A6, 'GPT-5 Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F6" s="31">
@@ -11084,15 +11084,15 @@
         <v/>
       </c>
       <c r="C7" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$44, $A7, 'GPT-5 Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D7" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$45:$A$51, $A7, 'GPT-5 Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A7, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E7" s="31">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$44, $A7, 'GPT-5 Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F7" s="31">
@@ -11124,15 +11124,15 @@
         <v/>
       </c>
       <c r="C8" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$44, $A8, 'GPT-5 Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D8" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$45:$A$51, $A8, 'GPT-5 Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A8, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E8" s="31">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$44, $A8, 'GPT-5 Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F8" s="31">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="J8" s="69" t="inlineStr">
         <is>
-          <t>Gemini</t>
+          <t>Gemini 3.1 Pro</t>
         </is>
       </c>
     </row>
@@ -11164,15 +11164,15 @@
         <v/>
       </c>
       <c r="C9" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$2:$A$44, $A9, 'GPT-5 Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D9" s="31">
-        <f>SUMIF('GPT-5 Generation'!$A$45:$A$51, $A9, 'GPT-5 Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A9, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E9" s="31">
-        <f>COUNTIFS('GPT-5 Generation'!$A$2:$A$44, $A9, 'GPT-5 Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F9" s="31">

--- a/Thermomix TM6/Grading/2 stage/6-examples/Thermomix-TM6_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
+++ b/Thermomix TM6/Grading/2 stage/6-examples/Thermomix-TM6_Grading_2-stage_2026-03-12_6-examples_Gemini3.1ProPreviewGeneration_Gemini3.1ProPreviewAutoGrading.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Thermonix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Gemini 3.1 Pro Generation" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Gemini 3.1 Pro Grading" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Metrics" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -10932,15 +10932,15 @@
         <v/>
       </c>
       <c r="C3" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D3" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A3, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$45:$A$51, $A3, 'Gemini 3.1 Pro Grading'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E3" s="31">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A3, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A3, 'Gemini 3.1 Pro Grading'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F3" s="31">
@@ -10968,15 +10968,15 @@
         <v/>
       </c>
       <c r="C4" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D4" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A4, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$45:$A$51, $A4, 'Gemini 3.1 Pro Grading'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E4" s="31">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A4, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A4, 'Gemini 3.1 Pro Grading'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F4" s="31">
@@ -11008,15 +11008,15 @@
         <v/>
       </c>
       <c r="C5" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D5" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A5, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$45:$A$51, $A5, 'Gemini 3.1 Pro Grading'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E5" s="31">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A5, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A5, 'Gemini 3.1 Pro Grading'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F5" s="31">
@@ -11048,15 +11048,15 @@
         <v/>
       </c>
       <c r="C6" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D6" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A6, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$45:$A$51, $A6, 'Gemini 3.1 Pro Grading'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E6" s="31">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A6, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A6, 'Gemini 3.1 Pro Grading'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F6" s="31">
@@ -11084,15 +11084,15 @@
         <v/>
       </c>
       <c r="C7" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D7" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A7, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$45:$A$51, $A7, 'Gemini 3.1 Pro Grading'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E7" s="31">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A7, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A7, 'Gemini 3.1 Pro Grading'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F7" s="31">
@@ -11124,15 +11124,15 @@
         <v/>
       </c>
       <c r="C8" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D8" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A8, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$45:$A$51, $A8, 'Gemini 3.1 Pro Grading'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E8" s="31">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A8, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A8, 'Gemini 3.1 Pro Grading'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F8" s="31">
@@ -11164,15 +11164,15 @@
         <v/>
       </c>
       <c r="C9" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$44)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$44)</f>
         <v/>
       </c>
       <c r="D9" s="31">
-        <f>SUMIF('Gemini 3.1 Pro Generation'!$A$45:$A$51, $A9, 'Gemini 3.1 Pro Generation'!$C$45:$C$51)</f>
+        <f>SUMIF('Gemini 3.1 Pro Grading'!$A$45:$A$51, $A9, 'Gemini 3.1 Pro Grading'!$C$45:$C$51)</f>
         <v/>
       </c>
       <c r="E9" s="31">
-        <f>COUNTIFS('Gemini 3.1 Pro Generation'!$A$2:$A$44, $A9, 'Gemini 3.1 Pro Generation'!$C$2:$C$44,0)</f>
+        <f>COUNTIFS('Gemini 3.1 Pro Grading'!$A$2:$A$44, $A9, 'Gemini 3.1 Pro Grading'!$C$2:$C$44,0)</f>
         <v/>
       </c>
       <c r="F9" s="31">
